--- a/docs/CAU_HOI_TEST_3_NGON_NGU.xlsx
+++ b/docs/CAU_HOI_TEST_3_NGON_NGU.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Hai con số khớp bảng Phân tích lệnh giao hàng (12/09: 11 đang chạy, 21 hoàn tất).</t>
+          <t>Hai con số khớp ĐÚNG ô 'Đang vận chuyển' và 'Hoàn thành' trên bảng Phân tích lệnh giao hàng. Đây là câu bẫy: đếm thô theo trạng thái sẽ ra số khác (gộp cả lệnh đã tới chờ ký).</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Đúng mã lệnh VÀ đúng tên khách (12/09: 2 lệnh DO-2026-0026, khách Samsung Electronics HCMC CE). Tên khách sai là LỖI NẶNG — xem mục 6.2 của tài liệu.</t>
+          <t>Đúng mã lệnh VÀ đúng tên khách (số ngày 12/09 là 2 lệnh DO-2026-0026, khách Samsung Electronics HCMC CE — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình). Tên khách sai là LỖI NẶNG — xem mục 6.2 của tài liệu.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Nhóm Gần trễ, kèm mã lệnh và hạn giao (12/09: 1 lệnh).</t>
+          <t>Nhóm Gần trễ, kèm mã lệnh và hạn giao (số ngày 12/09 là 1 lệnh — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình).</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Con số khớp nhóm Chờ vận chuyển (12/09: 13).</t>
+          <t>Con số khớp ĐÚNG ô 'Chờ vận chuyển' trên bảng. Bẫy: đếm thô trạng thái pending sẽ cao hơn, vì bảng đã tách các lệnh quá hạn và gần trễ ra khỏi ô này.</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>chuyen_dang_chay</t>
+          <t>chuyen_dang_chay · xe</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Danh sách chuyến đang chạy kèm biển số, tài xế, tuyến (12/09: 16 dòng, 12 xe).</t>
+          <t>Danh sách chuyến đang chạy kèm biển số, tài xế, tuyến. Số xe khớp ô 'vehicles' của Tháp kiểm soát; một xe có thể chở nhiều lệnh nên số dòng lớn hơn số xe.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Đúng số chuyến chờ ký (12/09: 5), kèm tài xế và khách.</t>
+          <t>Đúng số chuyến chờ ký (số ngày 12/09 là 5 — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình), kèm tài xế và khách.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>chuyen · xe</t>
+          <t>chuyen_dang_chay · chuyen · xe</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>5 sự cố (12/09) kèm loại, mức độ, vị trí, mã lệnh, xe.</t>
+          <t>5 sự cố (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này) kèm loại, mức độ, vị trí, mã lệnh, xe.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>bao_gia</t>
+          <t>bao_gia · tong_quan_hom_nay</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Khớp tóm lược báo giá (12/09: 56 đang mở).</t>
+          <t>Khớp tóm lược báo giá (số ngày 12/09 là 56 đang mở — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình).</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Trạng thái đã gửi khách (12/09: 9), kèm mã và khách.</t>
+          <t>Trạng thái đã gửi khách (số ngày 12/09 là 9 — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình), kèm mã và khách.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Đọc được ngưỡng (15%) và đếm đúng (12/09: 4).</t>
+          <t>Đọc được ngưỡng (15%) và đếm đúng (số ngày 12/09 là 4 — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình).</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>91,3% (12/09) — dạng phần trăm, không phải 0.913.</t>
+          <t>91,3% (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này) — dạng phần trăm, không phải 0.913.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>19 đang mở (12/09), chia theo sáu giai đoạn, dùng tên giai đoạn tiếng Việt.</t>
+          <t>19 đang mở (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này), chia theo sáu giai đoạn, dùng tên giai đoạn tiếng Việt.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Giai đoạn Đã báo giá (12/09: 14), kèm khách và mã báo giá.</t>
+          <t>Giai đoạn Đã báo giá (số ngày 12/09 là 14 — dữ liệu làm tươi mỗi buổi, hãy đối chiếu màn hình), kèm khách và mã báo giá.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>khach_hang</t>
+          <t>doanh_thu · khach_hang</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>15 (12/09).</t>
+          <t>15 (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này).</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>12/09: 0 xe rảnh, 4 tài xế rảnh — nói thẳng 0 xe, không né.</t>
+          <t>Ngày 12/09 là: 0 xe rảnh, 4 tài xế rảnh — nói thẳng 0 xe, không né.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>3 xe (12/09) kèm biển số, ngày hết hạn, còn mấy ngày.</t>
+          <t>3 xe (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này) kèm biển số, ngày hết hạn, còn mấy ngày.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>12/09: 0 — phải nói không có, không bịa ra xe.</t>
+          <t>Ngày 12/09 là: 0 — phải nói không có, không bịa ra xe.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>8 tuyến (12/09).</t>
+          <t>8 tuyến (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này).</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1 LAK = 1,18 VNĐ (12/09), nói rõ chiều quy đổi.</t>
+          <t>1 LAK = 1,18 VNĐ (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này), nói rõ chiều quy đổi.</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>21 (12/09).</t>
+          <t>21 (số của ngày 12/09; đối chiếu màn hình chứ đừng chấm theo con số này).</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ho_so_hoan_tat · chi_tiet_hoan_tat</t>
+          <t>doanh_thu · ho_so_hoan_tat · chi_tiet_hoan_tat</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ho_so_khach_hang</t>
+          <t>(không gọi — trả lời từ trí nhớ)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -3801,17 +3801,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Bật máy chủ EPL</t>
+          <t>Kiểm máy chủ EPL đã host</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Ở D:\Demo_Lao\EPL_System chạy: python -m uvicorn backend.app.main:app --host 0.0.0.0 --port 8001 --no-access-log</t>
+          <t>Mở http://senvangsolutions.com:1506/api/health — trợ lý mặc định hỏi máy chủ này, không cần bật gì trên máy mình</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Log hiện 'Application startup complete'. Mở http://localhost:8001 thấy hệ EPL.</t>
+          <t>Trả về {"status":"ok"}. Nếu không mở được thì kiểm đường mạng trước khi làm tiếp.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -4395,17 +4395,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Tắt máy chủ EPL giữa chừng</t>
+          <t>Mất kết nối tới máy chủ EPL</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Tắt cửa sổ chạy EPL (cổng 8001), rồi hỏi một câu bất kỳ</t>
+          <t>Bật trợ lý với --api trỏ vào một cổng KHÔNG có gì chạy (ví dụ python chay.py --api http://127.0.0.1:8001 khi chưa bật uvicorn), rồi hỏi một câu bất kỳ</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Đầu trang hiện 'Không nối được hệ thống EPL'; câu trả lời nói không lấy được dữ liệu — KHÔNG bịa số. Bật lại EPL thì hỏi lại chạy bình thường.</t>
+          <t>Đầu trang hiện 'Không nối được hệ thống EPL'; câu trả lời nói không lấy được dữ liệu — KHÔNG bịa số. Chạy lại trợ lý không có --api (về 1506) thì hỏi lại chạy bình thường.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
